--- a/data/trans_orig/IP38E_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39880</t>
+          <t>39534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>47357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>53887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96180</t>
+          <t>96277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106359</t>
+          <t>106756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37355</t>
+          <t>36902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52183</t>
+          <t>52079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57412</t>
+          <t>57317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91243</t>
+          <t>91608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107855</t>
+          <t>107801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24752</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55500</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65806</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71895</t>
+          <t>71673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>85526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131265</t>
+          <t>131483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148394</t>
+          <t>148982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>21336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157227</t>
+          <t>157476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>176004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>202587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>220907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>368685</t>
+          <t>368776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>394305</t>
+          <t>392975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>64706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP38E_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16768</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13367</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18296</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15161</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12519</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16598</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>88,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20950</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36112</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>32599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18972</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18972</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18972</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17138</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17138</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17138</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>34269</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>34269</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>34269</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50163</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>46116</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52287</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>44303</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39534</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47357</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58234</t>
+          <t>38745</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53887</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60728</t>
+          <t>41711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>102536</t>
+          <t>88908</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96277</t>
+          <t>82918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106756</t>
+          <t>92639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>53905</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>49885</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>49885</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>49885</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>44293</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>44293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>44293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>112543</t>
+          <t>98198</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112543</t>
+          <t>98198</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112543</t>
+          <t>98198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51540</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46516</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54192</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>82,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47332</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36902</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52079</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54521</t>
+          <t>49307</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57317</t>
+          <t>52829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>101853</t>
+          <t>100849</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>93601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107801</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9515</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4768</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19945</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56097</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56097</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56097</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>56847</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>56847</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56847</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115995</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115995</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115995</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79215</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>71045</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>84578</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>61451</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55389</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65631</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79930</t>
+          <t>65321</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71673</t>
+          <t>58564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85526</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>141381</t>
+          <t>144536</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131483</t>
+          <t>134714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148982</t>
+          <t>152105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12597</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7234</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20767</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10198</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6018</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16260</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23277</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>91812</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>91812</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>91812</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>71649</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>71649</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>71649</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93009</t>
+          <t>76127</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93009</t>
+          <t>76127</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93009</t>
+          <t>76127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>164658</t>
+          <t>167939</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>164658</t>
+          <t>167939</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>164658</t>
+          <t>167939</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>197686</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>187060</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>203898</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>84,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>168247</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>157476</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>176004</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>86,05%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>80,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202587</t>
+          <t>157881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220907</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>368776</t>
+          <t>352379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392975</t>
+          <t>376801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33726</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19515</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38043</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64706</t>
+          <t>60949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
